--- a/artfynd/A 42488-2022 artfynd.xlsx
+++ b/artfynd/A 42488-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42488-2022 artfynd.xlsx
+++ b/artfynd/A 42488-2022 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>104350087</v>
       </c>
       <c r="B12" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380190.7227334208</v>
+        <v>380190</v>
       </c>
       <c r="R12" t="n">
-        <v>6743023.05914304</v>
+        <v>6743023</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1868,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 42488-2022 artfynd.xlsx
+++ b/artfynd/A 42488-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104350650</v>
+        <v>104350063</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>N om Ömtbergets NR, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380250.2146549472</v>
+        <v>380119</v>
       </c>
       <c r="R2" t="n">
-        <v>6742959.03262769</v>
+        <v>6742899</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104350654</v>
+        <v>104350651</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380220.6958922637</v>
+        <v>380253</v>
       </c>
       <c r="R3" t="n">
-        <v>6742939.508891194</v>
+        <v>6742958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104350637</v>
+        <v>104350653</v>
       </c>
       <c r="B4" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380167.7696139141</v>
+        <v>380249</v>
       </c>
       <c r="R4" t="n">
-        <v>6743009.66536135</v>
+        <v>6742952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104350648</v>
+        <v>104350650</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380254.3180276032</v>
+        <v>380250</v>
       </c>
       <c r="R5" t="n">
-        <v>6742950.103210086</v>
+        <v>6742959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104350635</v>
+        <v>104350071</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>N om Ömtbergets NR, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380202.6607565928</v>
+        <v>380268</v>
       </c>
       <c r="R6" t="n">
-        <v>6743014.355268791</v>
+        <v>6742970</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104350652</v>
+        <v>104350649</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380253.3734313039</v>
+        <v>380247</v>
       </c>
       <c r="R7" t="n">
-        <v>6742951.111761569</v>
+        <v>6742952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104350063</v>
+        <v>104350652</v>
       </c>
       <c r="B8" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N om Ömtbergets NR, Vrm</t>
+          <t>Norr om Ömtberget, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380119.0609955179</v>
+        <v>380253</v>
       </c>
       <c r="R8" t="n">
-        <v>6742899.449886479</v>
+        <v>6742951</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,19 +1325,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,62 +1342,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104350639</v>
+        <v>104350076</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>N om Ömtbergets NR, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380168.6486564708</v>
+        <v>380176</v>
       </c>
       <c r="R9" t="n">
-        <v>6743006.705302105</v>
+        <v>6742972</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,49 +1439,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104350649</v>
+        <v>104350634</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380247.5258197224</v>
+        <v>380216</v>
       </c>
       <c r="R10" t="n">
-        <v>6742951.796367095</v>
+        <v>6743018</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,50 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104350071</v>
+        <v>104350640</v>
       </c>
       <c r="B11" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N om Ömtbergets NR, Vrm</t>
+          <t>Norr om Ömtberget, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380268.1993143009</v>
+        <v>380165</v>
       </c>
       <c r="R11" t="n">
-        <v>6742970.151638175</v>
+        <v>6742961</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,62 +1633,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104350087</v>
+        <v>104350648</v>
       </c>
       <c r="B12" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N om Ömtbergets NR, Vrm</t>
+          <t>Norr om Ömtberget, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380190</v>
+        <v>380255</v>
       </c>
       <c r="R12" t="n">
-        <v>6743023</v>
+        <v>6742950</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,49 +1730,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104350651</v>
+        <v>104350655</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380253.1139042496</v>
+        <v>380207</v>
       </c>
       <c r="R13" t="n">
-        <v>6742957.958504017</v>
+        <v>6742900</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,19 +1810,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104350653</v>
+        <v>104350085</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,34 +1850,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6450</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>N om Ömtbergets NR, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380249.4804792034</v>
+        <v>380087</v>
       </c>
       <c r="R14" t="n">
-        <v>6742951.73079169</v>
+        <v>6742844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2082,19 +1907,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,27 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104350636</v>
+        <v>104350086</v>
       </c>
       <c r="B15" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2137,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norr om Ömtberget, Vrm</t>
+          <t>N om Ömtbergets NR, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380202.6607565928</v>
+        <v>380163</v>
       </c>
       <c r="R15" t="n">
-        <v>6743014.355268791</v>
+        <v>6742945</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2194,19 +2004,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,27 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104350634</v>
+        <v>104350636</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2273,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380215.4804281608</v>
+        <v>380202</v>
       </c>
       <c r="R16" t="n">
-        <v>6743017.344002469</v>
+        <v>6743014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2306,19 +2101,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2345,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104350655</v>
+        <v>104350639</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2385,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380207.1530053866</v>
+        <v>380169</v>
       </c>
       <c r="R17" t="n">
-        <v>6742900.400019333</v>
+        <v>6743007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2418,19 +2198,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2457,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104350638</v>
+        <v>104350654</v>
       </c>
       <c r="B18" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380167.7696139141</v>
+        <v>380220</v>
       </c>
       <c r="R18" t="n">
-        <v>6743009.66536135</v>
+        <v>6742939</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2530,19 +2295,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,50 +2324,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104350078</v>
+        <v>104350638</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>N om Ömtbergets NR, Vrm</t>
+          <t>Norr om Ömtberget, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380263.8502763003</v>
+        <v>380168</v>
       </c>
       <c r="R19" t="n">
-        <v>6743073.84295321</v>
+        <v>6743010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2642,19 +2392,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,49 +2409,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104350084</v>
+        <v>104350087</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2721,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380284.3779806754</v>
+        <v>380190</v>
       </c>
       <c r="R20" t="n">
-        <v>6743102.459162759</v>
+        <v>6743023</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2754,19 +2489,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2790,6 +2515,704 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>104350078</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>N om Ömtbergets NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>380264</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6743074</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>104350084</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>N om Ömtbergets NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>380285</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6743102</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>105000900</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ömtbergets NR, N om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>380284</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6743102</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>S-Tor-0338</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Även vid RT90: 6746884 - 1336410.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104350070</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>N om Ömtbergets NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>380270</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6743078</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104350077</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>N om Ömtbergets NR, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>380171</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6742962</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104350635</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norr om Ömtberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>380202</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6743014</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104350637</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norr om Ömtberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>380168</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6743010</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42488-2022 artfynd.xlsx
+++ b/artfynd/A 42488-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350063</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350651</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350653</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350650</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350071</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350649</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350652</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350076</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350634</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350640</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350648</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350655</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350086</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350636</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350639</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350654</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350638</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350087</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350078</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350084</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2825,6 +2935,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105000900</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2922,6 +3037,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350070</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3019,6 +3139,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350077</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3116,6 +3241,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350635</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3213,8 +3343,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104350637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>